--- a/merchant_forms/042_merchant_services_application_form--merchant_forms.xlsx
+++ b/merchant_forms/042_merchant_services_application_form--merchant_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>merchant_address</t>
+          <t>merchant_address_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Merchant Address</t>
+          <t>Merchant Address 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>submitted_by</t>
+          <t>submitted_by_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Submitted By</t>
+          <t>Submitted By 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>submitted_date</t>
+          <t>submitted_date_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Submitted Date</t>
+          <t>Submitted Date 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>submitted_time</t>
+          <t>submitted_time_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Submitted Time</t>
+          <t>Submitted Time 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>merchant_services</t>
+          <t>merchant_services_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Merchant Services</t>
+          <t>Merchant Services 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1029,7 +1029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -1249,12 +1249,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1266,12 +1266,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1283,131 +1283,63 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>submitted_choices</t>
+          <t>merchant_services_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option_4</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Option 4</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>submitted_choices</t>
+          <t>merchant_services_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option_5</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Option 5</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>merchant_services_choices</t>
+          <t>merchant_services_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Option 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>merchant_services_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>option_2</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Option 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>merchant_services_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>option_3</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Option 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>merchant_services_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>option_4</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Option 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>merchant_services_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>option_5</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Option 5</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
